--- a/Codes_2025/Trial 3/Trial3_RF_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_RF_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>22.34</v>
       </c>
       <c r="D2" t="n">
-        <v>18.62138100729934</v>
+        <v>19.55257363917519</v>
       </c>
       <c r="E2" t="n">
-        <v>3.718618992700659</v>
+        <v>2.787426360824803</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>35.4</v>
       </c>
       <c r="D3" t="n">
-        <v>20.37722267440405</v>
+        <v>18.31111711635399</v>
       </c>
       <c r="E3" t="n">
-        <v>15.02277732559595</v>
+        <v>17.088882883646</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         <v>6.549999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>17.79377558100645</v>
+        <v>18.39603520118162</v>
       </c>
       <c r="E4" t="n">
-        <v>11.24377558100645</v>
+        <v>11.84603520118162</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>69.53000000000007</v>
       </c>
       <c r="D5" t="n">
-        <v>33.48314635141914</v>
+        <v>32.60295863808157</v>
       </c>
       <c r="E5" t="n">
-        <v>36.04685364858094</v>
+        <v>36.9270413619185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>21.01</v>
+        <v>37.81</v>
       </c>
       <c r="D6" t="n">
-        <v>19.34933569615712</v>
+        <v>19.33380921311667</v>
       </c>
       <c r="E6" t="n">
-        <v>1.660664303842879</v>
+        <v>18.47619078688334</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>20.08</v>
+        <v>21.01</v>
       </c>
       <c r="D7" t="n">
-        <v>23.90580867260126</v>
+        <v>21.64664006103454</v>
       </c>
       <c r="E7" t="n">
-        <v>3.825808672601266</v>
+        <v>0.6366400610345337</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D8" t="n">
-        <v>17.98702694541068</v>
+        <v>24.78463136676546</v>
       </c>
       <c r="E8" t="n">
-        <v>8.62702694541068</v>
+        <v>4.704631366765462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>7.180000000000001</v>
+        <v>6.81</v>
       </c>
       <c r="D9" t="n">
-        <v>18.60241881542675</v>
+        <v>19.80026993425165</v>
       </c>
       <c r="E9" t="n">
-        <v>11.42241881542675</v>
+        <v>12.99026993425165</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>37.67999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01979149339438</v>
+        <v>18.33753222802336</v>
       </c>
       <c r="E10" t="n">
-        <v>2.660208506605613</v>
+        <v>8.97753222802336</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>11.85320524280488</v>
+        <v>20.92050384968109</v>
       </c>
       <c r="E11" t="n">
-        <v>4.123205242804883</v>
+        <v>13.74050384968109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.590000000000001</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>12.92016563185457</v>
+        <v>36.77262060808065</v>
       </c>
       <c r="E12" t="n">
-        <v>6.330165631854572</v>
+        <v>0.907379391919342</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>10.19</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="n">
-        <v>11.85090959107335</v>
+        <v>12.26593826976453</v>
       </c>
       <c r="E13" t="n">
-        <v>1.66090959107335</v>
+        <v>4.53593826976453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,22 +751,94 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.26000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18.95629147996629</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.30370852003372</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.80741008036006</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.21741008036006</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14.0816865257297</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.891686525729705</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>37.58000000000002</v>
       </c>
-      <c r="D14" t="n">
-        <v>11.61153758234464</v>
-      </c>
-      <c r="E14" t="n">
-        <v>25.96846241765538</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D17" t="n">
+        <v>10.58951166345232</v>
+      </c>
+      <c r="E17" t="n">
+        <v>26.99048833654771</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Leaders</t>
         </is>
